--- a/Result/profitability/1444.xlsx
+++ b/Result/profitability/1444.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07500000000000001</v>
+        <v>-0.05625000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7925</v>
+        <v>4.06625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.03250000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>5.0525</v>
+        <v>4.98</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02750000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>5.32375</v>
+        <v>5.43375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.76</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.13125</v>
+        <v>-0.08375</v>
       </c>
       <c r="N5" t="n">
-        <v>4.73</v>
+        <v>4.615</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08624999999999999</v>
+        <v>-0.035</v>
       </c>
       <c r="N6" t="n">
-        <v>5.24375</v>
+        <v>5.68625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.01375000000000001</v>
+        <v>0.007499999999999996</v>
       </c>
       <c r="N7" t="n">
-        <v>6.31625</v>
+        <v>6.12125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1394,7 +1394,7 @@
         <v>0.007499999999999996</v>
       </c>
       <c r="N8" t="n">
-        <v>6.85</v>
+        <v>6.545</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.06875000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>8.411250000000001</v>
+        <v>8.411249999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9838,6 +9838,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1444</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2355</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2283</v>
+      </c>
+      <c r="E75" t="n">
+        <v>71</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-49</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>103</v>
+      </c>
+      <c r="J75" t="n">
+        <v>54</v>
+      </c>
+      <c r="K75" t="n">
+        <v>71</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.08875000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2.89125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4460694698354661</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.225806451612903</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9200000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2329113924050634</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
